--- a/IPC_Clase.xlsx
+++ b/IPC_Clase.xlsx
@@ -511,10 +511,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>0.08780247770477553</v>
+        <v>0.08780247770477552</v>
       </c>
       <c r="C2" s="2">
-        <v>118.5054491728023</v>
+        <v>118.5054491728022</v>
       </c>
       <c r="D2" s="2">
         <v>0.08780247770477552</v>
@@ -528,7 +528,7 @@
         <v>0.1033847267170256</v>
       </c>
       <c r="C3" s="2">
-        <v>110.0874006100097</v>
+        <v>110.0874006100098</v>
       </c>
       <c r="D3" s="2">
         <v>0.1033847267170256</v>
@@ -539,13 +539,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>0.008272185567809251</v>
+        <v>0.008272185567809252</v>
       </c>
       <c r="C4" s="2">
         <v>116.277059493863</v>
       </c>
       <c r="D4" s="2">
-        <v>0.008272185567809249</v>
+        <v>0.008272185567809252</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -553,13 +553,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>0.02922056077925974</v>
+        <v>0.02922056077925975</v>
       </c>
       <c r="C5" s="2">
         <v>114.6201453110841</v>
       </c>
       <c r="D5" s="2">
-        <v>0.02922056077925974</v>
+        <v>0.02922056077925975</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -587,7 +587,7 @@
         <v>109.9491593243103</v>
       </c>
       <c r="D7" s="2">
-        <v>0.03894224481106809</v>
+        <v>0.0389422448110681</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -595,13 +595,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>0.07357326095633684</v>
+        <v>0.07357326095633686</v>
       </c>
       <c r="C8" s="2">
-        <v>122.2954066875585</v>
+        <v>122.2954066875586</v>
       </c>
       <c r="D8" s="2">
-        <v>0.07357326095633683</v>
+        <v>0.07357326095633686</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -609,7 +609,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>0.008195531177283224</v>
+        <v>0.008195531177283222</v>
       </c>
       <c r="C9" s="2">
         <v>111.1494433963084</v>
@@ -623,13 +623,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>0.05497980878555928</v>
+        <v>0.05497980878555925</v>
       </c>
       <c r="C10" s="2">
         <v>111.4591370690855</v>
       </c>
       <c r="D10" s="2">
-        <v>0.05497980878555926</v>
+        <v>0.05497980878555925</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -637,13 +637,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>0.00794726616415295</v>
+        <v>0.007947266164152951</v>
       </c>
       <c r="C11" s="2">
         <v>106.0362070688473</v>
       </c>
       <c r="D11" s="2">
-        <v>0.007947266164152948</v>
+        <v>0.007947266164152951</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -651,13 +651,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>0.002771663492127025</v>
+        <v>0.002771663492127026</v>
       </c>
       <c r="C12" s="2">
         <v>110.2608888292721</v>
       </c>
       <c r="D12" s="2">
-        <v>0.002771663492127025</v>
+        <v>0.002771663492127026</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -671,7 +671,7 @@
         <v>140.1677028555776</v>
       </c>
       <c r="D13" s="2">
-        <v>0.004287135021955556</v>
+        <v>0.004287135021955557</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -685,7 +685,7 @@
         <v>130.3266217145816</v>
       </c>
       <c r="D14" s="2">
-        <v>0.002239187229884927</v>
+        <v>0.002239187229884928</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -699,7 +699,7 @@
         <v>122.5725893240119</v>
       </c>
       <c r="D15" s="2">
-        <v>0.00056417485769088</v>
+        <v>0.0005641748576908801</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -713,7 +713,7 @@
         <v>124.9914840788052</v>
       </c>
       <c r="D16" s="2">
-        <v>0.003340150088683028</v>
+        <v>0.003340150088683029</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -721,13 +721,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>0.05794652593417019</v>
+        <v>0.0579465259341702</v>
       </c>
       <c r="C17" s="2">
         <v>104.519639686742</v>
       </c>
       <c r="D17" s="2">
-        <v>0.05794652593417018</v>
+        <v>0.0579465259341702</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -755,7 +755,7 @@
         <v>101.4577216846236</v>
       </c>
       <c r="D19" s="2">
-        <v>0.003123825722659979</v>
+        <v>0.00312382572265998</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -769,7 +769,7 @@
         <v>110.8349620633415</v>
       </c>
       <c r="D20" s="2">
-        <v>0.1318165889190015</v>
+        <v>0.1318165889190016</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -794,7 +794,7 @@
         <v>0.02010526075751034</v>
       </c>
       <c r="C22" s="2">
-        <v>113.1127432298365</v>
+        <v>113.1127432298366</v>
       </c>
       <c r="D22" s="2">
         <v>0.02010526075751034</v>
@@ -811,7 +811,7 @@
         <v>115.1721115220231</v>
       </c>
       <c r="D23" s="2">
-        <v>0.01473634156175831</v>
+        <v>0.01473634156175832</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -819,13 +819,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2">
-        <v>0.006418384312982259</v>
+        <v>0.006418384312982258</v>
       </c>
       <c r="C24" s="2">
         <v>104.3548762651075</v>
       </c>
       <c r="D24" s="2">
-        <v>0.006418384312982257</v>
+        <v>0.006418384312982258</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -853,7 +853,7 @@
         <v>120.0345653810588</v>
       </c>
       <c r="D26" s="2">
-        <v>0.004618478267239091</v>
+        <v>0.004618478267239092</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -861,7 +861,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="2">
-        <v>0.005255964301810134</v>
+        <v>0.005255964301810133</v>
       </c>
       <c r="C27" s="2">
         <v>123.2904970359778</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0511185110208276</v>
+        <v>0.05111851102082762</v>
       </c>
       <c r="C28" s="2">
-        <v>128.7319396570368</v>
+        <v>128.7319396570367</v>
       </c>
       <c r="D28" s="2">
-        <v>0.05111851102082758</v>
+        <v>0.05111851102082762</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -903,13 +903,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02249321844136256</v>
+        <v>0.02249321844136257</v>
       </c>
       <c r="C30" s="2">
-        <v>116.7768227730314</v>
+        <v>116.7768227730315</v>
       </c>
       <c r="D30" s="2">
-        <v>0.02249321844136256</v>
+        <v>0.02249321844136257</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -917,13 +917,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2">
-        <v>0.003063062324578662</v>
+        <v>0.003063062324578663</v>
       </c>
       <c r="C31" s="2">
         <v>103.3156397339718</v>
       </c>
       <c r="D31" s="2">
-        <v>0.003063062324578661</v>
+        <v>0.003063062324578663</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -931,7 +931,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="2">
-        <v>0.01283849732236524</v>
+        <v>0.01283849732236523</v>
       </c>
       <c r="C32" s="2">
         <v>101.0725826868128</v>
@@ -945,13 +945,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>0.003751833951558037</v>
+        <v>0.003751833951558038</v>
       </c>
       <c r="C33" s="2">
         <v>106.4360311198445</v>
       </c>
       <c r="D33" s="2">
-        <v>0.003751833951558036</v>
+        <v>0.003751833951558038</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -962,10 +962,10 @@
         <v>0.01163183974330734</v>
       </c>
       <c r="C34" s="2">
-        <v>100.6622583955598</v>
+        <v>100.6622583955599</v>
       </c>
       <c r="D34" s="2">
-        <v>0.01163183974330733</v>
+        <v>0.01163183974330734</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -976,7 +976,7 @@
         <v>0.005563922185213122</v>
       </c>
       <c r="C35" s="2">
-        <v>128.7324815389222</v>
+        <v>128.7324815389223</v>
       </c>
       <c r="D35" s="2">
         <v>0.005563922185213122</v>
@@ -990,7 +990,7 @@
         <v>0.02337999567124581</v>
       </c>
       <c r="C36" s="2">
-        <v>101.699913487983</v>
+        <v>101.6999134879831</v>
       </c>
       <c r="D36" s="2">
         <v>0.02337999567124581</v>
